--- a/docs/huyvu/XNT_HuyVu_2023.xlsx
+++ b/docs/huyvu/XNT_HuyVu_2023.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IT-001</t>
+          <t>OTH-010</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Màn hình máy tính &amp; Tivi</t>
+          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -3003,10 +3003,10 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>18182</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3015,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>18182</v>
       </c>
     </row>
     <row r="67">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IT-003</t>
+          <t>OTH-073</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Máy quét văn bản (Scanner)</t>
+          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -3066,304 +3066,70 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VP-050</t>
+          <t>SRV-002</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nội thất &amp; Thiết bị văn phòng</t>
+          <t>Dịch vụ &amp; Thi công - 2025</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>-29</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>-81475937</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="G68" t="n">
-        <v>43349091</v>
+        <v>130000</v>
       </c>
       <c r="H68" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>124825028</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>-58</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>-162951874</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>OTH-085</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Thiết bị liên lạc vô tuyến</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tổng cộng</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>20530933537</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1029.89</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1521774592</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>833</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>919511396</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>207.89</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OTH-005</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Phí chuyển phát nhanh &amp; Giao nhận Logistics</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>OTH-010</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>18182</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>1</v>
-      </c>
-      <c r="K71" t="n">
-        <v>18182</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>OTH-067</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Máy đếm tiền &amp; Thiết bị kiểm định tài chính</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OTH-073</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>SRV-002</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Dịch vụ &amp; Thi công - 2025</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" t="n">
-        <v>10</v>
-      </c>
-      <c r="G74" t="n">
-        <v>130000</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>10</v>
-      </c>
-      <c r="K74" t="n">
-        <v>130000</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Tổng cộng</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="n">
-        <v>-18</v>
-      </c>
-      <c r="E75" t="n">
-        <v>20449457600</v>
-      </c>
-      <c r="F75" t="n">
-        <v>1075.89</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1565123683</v>
-      </c>
-      <c r="H75" t="n">
-        <v>908</v>
-      </c>
-      <c r="I75" t="n">
-        <v>1044336424</v>
-      </c>
-      <c r="J75" t="n">
-        <v>149.89</v>
-      </c>
-      <c r="K75" t="n">
-        <v>20970244859</v>
+        <v>21133196733</v>
       </c>
     </row>
   </sheetData>
@@ -3377,7 +3143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5795,7 +5561,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>-20054546</v>
+        <v>-10027273</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -5813,7 +5579,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>-20054546</v>
+        <v>-10027273</v>
       </c>
     </row>
     <row r="63">
@@ -5834,7 +5600,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>-1636363.279999999</v>
+        <v>-818181.6399999997</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -5852,7 +5618,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>-1636363.279999999</v>
+        <v>-818181.6399999997</v>
       </c>
     </row>
     <row r="64">
@@ -5870,10 +5636,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>382</v>
+        <v>191</v>
       </c>
       <c r="E64" t="n">
-        <v>212898303.52</v>
+        <v>106449151.76</v>
       </c>
       <c r="F64" t="n">
         <v>26</v>
@@ -5888,10 +5654,10 @@
         <v>24833603</v>
       </c>
       <c r="J64" t="n">
-        <v>371</v>
+        <v>180</v>
       </c>
       <c r="K64" t="n">
-        <v>208570357.52</v>
+        <v>102121205.76</v>
       </c>
     </row>
     <row r="65">
@@ -5912,7 +5678,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>-3805364</v>
+        <v>-1902682</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -5930,7 +5696,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>-3805364</v>
+        <v>-1902682</v>
       </c>
     </row>
     <row r="66">
@@ -5939,25 +5705,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IT-001</t>
+          <t>OTH-010</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Màn hình máy tính &amp; Tivi</t>
+          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E66" t="n">
-        <v>-20054546</v>
+        <v>381816</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>54545</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -5966,10 +5732,10 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K66" t="n">
-        <v>-20054546</v>
+        <v>436361</v>
       </c>
     </row>
     <row r="67">
@@ -5978,19 +5744,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IT-003</t>
+          <t>OTH-073</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Máy quét văn bản (Scanner)</t>
+          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>-1636363.279999999</v>
+        <v>2030910</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -6005,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>-1636363.279999999</v>
+        <v>2030910</v>
       </c>
     </row>
     <row r="68">
@@ -6017,304 +5783,70 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VP-050</t>
+          <t>SRV-002</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nội thất &amp; Thiết bị văn phòng</t>
+          <t>Dịch vụ &amp; Thi công - 2025</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>371</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>208570357.52</v>
+        <v>130000</v>
       </c>
       <c r="F68" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>20505657</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>24833603</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>360</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>204242411.52</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>OTH-085</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Thiết bị liên lạc vô tuyến</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tổng cộng</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>6956.25</v>
       </c>
       <c r="E69" t="n">
-        <v>-3805364</v>
+        <v>22295544281.09</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1402.83</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1072302734.82</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>865775</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1527135026</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>-857415.9199999999</v>
       </c>
       <c r="K69" t="n">
-        <v>-3805364</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OTH-005</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Phí chuyển phát nhanh &amp; Giao nhận Logistics</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>OTH-010</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>9</v>
-      </c>
-      <c r="E71" t="n">
-        <v>381816</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>54545</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>10</v>
-      </c>
-      <c r="K71" t="n">
-        <v>436361</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>OTH-067</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Máy đếm tiền &amp; Thiết bị kiểm định tài chính</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OTH-073</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>2</v>
-      </c>
-      <c r="E73" t="n">
-        <v>2030910</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>2</v>
-      </c>
-      <c r="K73" t="n">
-        <v>2030910</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>SRV-002</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Dịch vụ &amp; Thi công - 2025</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10</v>
-      </c>
-      <c r="E74" t="n">
-        <v>130000</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>10</v>
-      </c>
-      <c r="K74" t="n">
-        <v>130000</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Tổng cộng</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="n">
-        <v>7518.25</v>
-      </c>
-      <c r="E75" t="n">
-        <v>22572319380.45</v>
-      </c>
-      <c r="F75" t="n">
-        <v>1428.83</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1092808391.82</v>
-      </c>
-      <c r="H75" t="n">
-        <v>865812</v>
-      </c>
-      <c r="I75" t="n">
-        <v>1551968629</v>
-      </c>
-      <c r="J75" t="n">
-        <v>-856864.9199999999</v>
-      </c>
-      <c r="K75" t="n">
-        <v>22113159143.27</v>
+        <v>21840711989.91</v>
       </c>
     </row>
   </sheetData>
@@ -6328,7 +5860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8746,7 +8278,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>-20054546</v>
+        <v>-10027273</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -8764,7 +8296,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>-20054546</v>
+        <v>-10027273</v>
       </c>
     </row>
     <row r="63">
@@ -8785,7 +8317,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>-1636363.279999999</v>
+        <v>-818181.6399999997</v>
       </c>
       <c r="F63" t="n">
         <v>1</v>
@@ -8803,7 +8335,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>-3281818.279999999</v>
+        <v>-2463636.640000001</v>
       </c>
     </row>
     <row r="64">
@@ -8821,10 +8353,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="E64" t="n">
-        <v>204242411.52</v>
+        <v>102121205.76</v>
       </c>
       <c r="F64" t="n">
         <v>122</v>
@@ -8839,10 +8371,10 @@
         <v>39705052</v>
       </c>
       <c r="J64" t="n">
-        <v>457</v>
+        <v>277</v>
       </c>
       <c r="K64" t="n">
-        <v>279022311.45</v>
+        <v>176901105.69</v>
       </c>
     </row>
     <row r="65">
@@ -8863,7 +8395,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>-3805364</v>
+        <v>-1902682</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -8881,7 +8413,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>-3805364</v>
+        <v>-1902682</v>
       </c>
     </row>
     <row r="66">
@@ -8890,19 +8422,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IT-001</t>
+          <t>OTH-010</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Màn hình máy tính &amp; Tivi</t>
+          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E66" t="n">
-        <v>-20054546</v>
+        <v>436361</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -8917,10 +8449,10 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K66" t="n">
-        <v>-20054546</v>
+        <v>436361</v>
       </c>
     </row>
     <row r="67">
@@ -8929,37 +8461,37 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IT-003</t>
+          <t>OTH-073</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Máy quét văn bản (Scanner)</t>
+          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>-3281818.279999999</v>
+        <v>2030910</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>17900000</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>19545455</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>-4927273.279999999</v>
+        <v>2030910</v>
       </c>
     </row>
     <row r="68">
@@ -8968,304 +8500,70 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VP-050</t>
+          <t>SRV-002</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nội thất &amp; Thiết bị văn phòng</t>
+          <t>Dịch vụ &amp; Thi công - 2025</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>457</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>279022311.45</v>
+        <v>130000</v>
       </c>
       <c r="F68" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>114484951.93</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>39705052</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>554</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>353802211.38</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>OTH-085</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Thiết bị liên lạc vô tuyến</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tổng cộng</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>-857415.9199999999</v>
       </c>
       <c r="E69" t="n">
-        <v>-3805364</v>
+        <v>21840711989.91</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1784.3</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1561250335.11</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>881</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1421835474</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>-856512.62</v>
       </c>
       <c r="K69" t="n">
-        <v>-3805364</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OTH-005</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Phí chuyển phát nhanh &amp; Giao nhận Logistics</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>OTH-010</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10</v>
-      </c>
-      <c r="E71" t="n">
-        <v>436361</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>10</v>
-      </c>
-      <c r="K71" t="n">
-        <v>436361</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>OTH-067</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Máy đếm tiền &amp; Thiết bị kiểm định tài chính</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OTH-073</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>2</v>
-      </c>
-      <c r="E73" t="n">
-        <v>2030910</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>2</v>
-      </c>
-      <c r="K73" t="n">
-        <v>2030910</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>SRV-002</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Dịch vụ &amp; Thi công - 2025</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10</v>
-      </c>
-      <c r="E74" t="n">
-        <v>130000</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>10</v>
-      </c>
-      <c r="K74" t="n">
-        <v>130000</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Tổng cộng</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="n">
-        <v>-856778.9199999999</v>
-      </c>
-      <c r="E75" t="n">
-        <v>22181965642.2</v>
-      </c>
-      <c r="F75" t="n">
-        <v>1907.3</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1693635287.04</v>
-      </c>
-      <c r="H75" t="n">
-        <v>907</v>
-      </c>
-      <c r="I75" t="n">
-        <v>1481085981</v>
-      </c>
-      <c r="J75" t="n">
-        <v>-855778.62</v>
-      </c>
-      <c r="K75" t="n">
-        <v>22394514948.24</v>
+        <v>21980126851.02</v>
       </c>
     </row>
   </sheetData>
@@ -9279,7 +8577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11697,7 +10995,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>-20054546</v>
+        <v>-10027273</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -11715,7 +11013,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>-20054546</v>
+        <v>-10027273</v>
       </c>
     </row>
     <row r="63">
@@ -11736,7 +11034,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>-4927273.279999999</v>
+        <v>-2463636.640000001</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -11754,7 +11052,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>-4927273.279999999</v>
+        <v>-2463636.640000001</v>
       </c>
     </row>
     <row r="64">
@@ -11772,10 +11070,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>554</v>
+        <v>277</v>
       </c>
       <c r="E64" t="n">
-        <v>353802211.38</v>
+        <v>176901105.69</v>
       </c>
       <c r="F64" t="n">
         <v>83</v>
@@ -11790,10 +11088,10 @@
         <v>161780703</v>
       </c>
       <c r="J64" t="n">
-        <v>414</v>
+        <v>137</v>
       </c>
       <c r="K64" t="n">
-        <v>264820589.38</v>
+        <v>87919483.69</v>
       </c>
     </row>
     <row r="65">
@@ -11814,7 +11112,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>-3805364</v>
+        <v>-1902682</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -11832,7 +11130,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>-3805364</v>
+        <v>-1902682</v>
       </c>
     </row>
     <row r="66">
@@ -11841,25 +11139,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IT-001</t>
+          <t>OTH-010</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Màn hình máy tính &amp; Tivi</t>
+          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E66" t="n">
-        <v>-20054546</v>
+        <v>436361</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>54545</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -11868,10 +11166,10 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K66" t="n">
-        <v>-20054546</v>
+        <v>490906</v>
       </c>
     </row>
     <row r="67">
@@ -11880,19 +11178,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IT-003</t>
+          <t>OTH-073</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Máy quét văn bản (Scanner)</t>
+          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>-4927273.279999999</v>
+        <v>2030910</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -11907,10 +11205,10 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>-4927273.279999999</v>
+        <v>2030910</v>
       </c>
     </row>
     <row r="68">
@@ -11919,304 +11217,70 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VP-050</t>
+          <t>SRV-002</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nội thất &amp; Thiết bị văn phòng</t>
+          <t>Dịch vụ &amp; Thi công - 2025</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>414</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>264820589.38</v>
+        <v>130000</v>
       </c>
       <c r="F68" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>72799081</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>161780703</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>274</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>175838967.38</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>OTH-085</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Thiết bị liên lạc vô tuyến</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tổng cộng</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>-856512.62</v>
       </c>
       <c r="E69" t="n">
-        <v>-3805364</v>
+        <v>21980126851.02</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>3757.62</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>2466758485.72</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>4382</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>3193876982</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>-857137</v>
       </c>
       <c r="K69" t="n">
-        <v>-3805364</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OTH-005</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Phí chuyển phát nhanh &amp; Giao nhận Logistics</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>OTH-010</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10</v>
-      </c>
-      <c r="E71" t="n">
-        <v>436361</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>54545</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>11</v>
-      </c>
-      <c r="K71" t="n">
-        <v>490906</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>OTH-067</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Máy đếm tiền &amp; Thiết bị kiểm định tài chính</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OTH-073</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>2</v>
-      </c>
-      <c r="E73" t="n">
-        <v>2030910</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>2</v>
-      </c>
-      <c r="K73" t="n">
-        <v>2030910</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>SRV-002</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Dịch vụ &amp; Thi công - 2025</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10</v>
-      </c>
-      <c r="E74" t="n">
-        <v>130000</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>10</v>
-      </c>
-      <c r="K74" t="n">
-        <v>130000</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Tổng cộng</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="n">
-        <v>-855821.62</v>
-      </c>
-      <c r="E75" t="n">
-        <v>22378667771.17</v>
-      </c>
-      <c r="F75" t="n">
-        <v>3840.62</v>
-      </c>
-      <c r="G75" t="n">
-        <v>2539557566.72</v>
-      </c>
-      <c r="H75" t="n">
-        <v>4605</v>
-      </c>
-      <c r="I75" t="n">
-        <v>3355657685</v>
-      </c>
-      <c r="J75" t="n">
-        <v>-856586</v>
-      </c>
-      <c r="K75" t="n">
-        <v>21562567652.89</v>
+        <v>21253008354.74</v>
       </c>
     </row>
   </sheetData>
@@ -13137,7 +12201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI75"/>
+  <dimension ref="A1:AI69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20013,7 +19077,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>-20054546</v>
+        <v>-10027273</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -20124,7 +19188,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>-4927273.279999999</v>
+        <v>-2463636.640000001</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -20214,10 +19278,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-29</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>-81475937</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
         <v>868</v>
@@ -20232,10 +19296,10 @@
         <v>609676243</v>
       </c>
       <c r="J64" t="n">
-        <v>274</v>
+        <v>137</v>
       </c>
       <c r="K64" t="n">
-        <v>175838967.38</v>
+        <v>87919483.69</v>
       </c>
       <c r="L64" t="n">
         <v>43349091</v>
@@ -20346,7 +19410,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>-3805364</v>
+        <v>-1902682</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -20427,12 +19491,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IT-001</t>
+          <t>OTH-010</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Màn hình máy tính &amp; Tivi</t>
+          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -20442,79 +19506,79 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G66" t="n">
-        <v>30909091</v>
+        <v>490906</v>
       </c>
       <c r="H66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>40936364</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K66" t="n">
-        <v>-20054546</v>
+        <v>490906</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>18182</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>6409091</v>
+        <v>18182</v>
       </c>
       <c r="O66" t="n">
-        <v>6900000</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>18182</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>54545</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>6409091</v>
+        <v>54545</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>54545</v>
       </c>
       <c r="W66" t="n">
-        <v>6900000</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>54545</v>
       </c>
       <c r="Y66" t="n">
         <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>54545</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>18090909</v>
+        <v>54545</v>
       </c>
       <c r="AC66" t="n">
-        <v>27136364</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>54545</v>
       </c>
       <c r="AE66" t="n">
         <v>0</v>
@@ -20526,7 +19590,7 @@
         <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>54545</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -20538,12 +19602,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IT-003</t>
+          <t>OTH-073</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Máy quét văn bản (Scanner)</t>
+          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -20553,22 +19617,22 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
+        <v>3</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3894546</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1863636</v>
+      </c>
+      <c r="J67" t="n">
         <v>2</v>
       </c>
-      <c r="G67" t="n">
-        <v>24263636.36</v>
-      </c>
-      <c r="H67" t="n">
-        <v>2</v>
-      </c>
-      <c r="I67" t="n">
-        <v>26727273</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
       <c r="K67" t="n">
-        <v>-4927273.279999999</v>
+        <v>2030910</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -20595,16 +19659,16 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>6363636.36</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>7181818</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>3226364</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1863636</v>
       </c>
       <c r="X67" t="n">
         <v>0</v>
@@ -20619,7 +19683,7 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>668182</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -20631,10 +19695,10 @@
         <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>17900000</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>19545455</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
         <v>0</v>
@@ -20649,880 +19713,214 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VP-050</t>
+          <t>SRV-002</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nội thất &amp; Thiết bị văn phòng</t>
+          <t>Dịch vụ &amp; Thi công - 2025</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>-29</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>-81475937</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>868</v>
+        <v>10</v>
       </c>
       <c r="G68" t="n">
-        <v>697595726.6900001</v>
+        <v>130000</v>
       </c>
       <c r="H68" t="n">
-        <v>731</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>609676243</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>274</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>175838967.38</v>
+        <v>130000</v>
       </c>
       <c r="L68" t="n">
-        <v>43349091</v>
+        <v>130000</v>
       </c>
       <c r="M68" t="n">
-        <v>124825028</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>87660377</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>9950909</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>32131899</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>50072728</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>105032302</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>43150003</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>67598785.94</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>32409091</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>55222141</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>21985455</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>30047814</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>27286363</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>42195283.82</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>58330034</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>26568343</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>15347274</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>20505657</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>24833603</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>114484951.93</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>39705052</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>72799081</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="n">
-        <v>161780703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>OTH-085</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Thiết bị liên lạc vô tuyến</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tổng cộng</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>20530933537</v>
       </c>
       <c r="F69" t="n">
-        <v>9</v>
+        <v>21153</v>
       </c>
       <c r="G69" t="n">
-        <v>2515500</v>
+        <v>16986037636.74</v>
       </c>
       <c r="H69" t="n">
-        <v>9</v>
+        <v>878301</v>
       </c>
       <c r="I69" t="n">
-        <v>4418182</v>
+        <v>16263962819</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>-857137</v>
       </c>
       <c r="K69" t="n">
-        <v>-3805364</v>
+        <v>21253008354.74</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1521774592</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>919511396</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1852892781</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>1195768183</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1546332254.63</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>1549732728</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>816733309.09</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>978168179</v>
       </c>
       <c r="T69" t="n">
-        <v>2515500</v>
+        <v>741740814.9</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>866282729</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>788999294.83</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>994051814</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>1053981801</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1163811820</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1802942624.82</v>
       </c>
       <c r="AA69" t="n">
-        <v>4418182</v>
+        <v>1166995591</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1760328608.82</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1286792897</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1072302734.82</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1527135026</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1561250335.11</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1421835474</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>2466758485.72</v>
       </c>
       <c r="AI69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OTH-005</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Phí chuyển phát nhanh &amp; Giao nhận Logistics</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>OTH-010</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="n">
-        <v>11</v>
-      </c>
-      <c r="G71" t="n">
-        <v>490906</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>11</v>
-      </c>
-      <c r="K71" t="n">
-        <v>490906</v>
-      </c>
-      <c r="L71" t="n">
-        <v>18182</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>18182</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>18182</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>54545</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>54545</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" t="n">
-        <v>54545</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0</v>
-      </c>
-      <c r="X71" t="n">
-        <v>54545</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>54545</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>54545</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>54545</v>
-      </c>
-      <c r="AE71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>54545</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>OTH-067</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Máy đếm tiền &amp; Thiết bị kiểm định tài chính</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" t="n">
-        <v>0</v>
-      </c>
-      <c r="X72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OTH-073</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="n">
-        <v>3</v>
-      </c>
-      <c r="G73" t="n">
-        <v>3894546</v>
-      </c>
-      <c r="H73" t="n">
-        <v>1</v>
-      </c>
-      <c r="I73" t="n">
-        <v>1863636</v>
-      </c>
-      <c r="J73" t="n">
-        <v>2</v>
-      </c>
-      <c r="K73" t="n">
-        <v>2030910</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" t="n">
-        <v>3226364</v>
-      </c>
-      <c r="W73" t="n">
-        <v>1863636</v>
-      </c>
-      <c r="X73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>668182</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI73" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>SRV-002</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Dịch vụ &amp; Thi công - 2025</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" t="n">
-        <v>10</v>
-      </c>
-      <c r="G74" t="n">
-        <v>130000</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>10</v>
-      </c>
-      <c r="K74" t="n">
-        <v>130000</v>
-      </c>
-      <c r="L74" t="n">
-        <v>130000</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" t="n">
-        <v>0</v>
-      </c>
-      <c r="V74" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" t="n">
-        <v>0</v>
-      </c>
-      <c r="X74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI74" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Tổng cộng</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="n">
-        <v>-47</v>
-      </c>
-      <c r="E75" t="n">
-        <v>20367981663</v>
-      </c>
-      <c r="F75" t="n">
-        <v>22035</v>
-      </c>
-      <c r="G75" t="n">
-        <v>17741321590.79</v>
-      </c>
-      <c r="H75" t="n">
-        <v>879046</v>
-      </c>
-      <c r="I75" t="n">
-        <v>16945720881</v>
-      </c>
-      <c r="J75" t="n">
-        <v>-856726</v>
-      </c>
-      <c r="K75" t="n">
-        <v>21473586030.89</v>
-      </c>
-      <c r="L75" t="n">
-        <v>1565123683</v>
-      </c>
-      <c r="M75" t="n">
-        <v>1044336424</v>
-      </c>
-      <c r="N75" t="n">
-        <v>1946962249</v>
-      </c>
-      <c r="O75" t="n">
-        <v>1212619092</v>
-      </c>
-      <c r="P75" t="n">
-        <v>1578464153.63</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>1599805456</v>
-      </c>
-      <c r="R75" t="n">
-        <v>921765611.09</v>
-      </c>
-      <c r="S75" t="n">
-        <v>1021318182</v>
-      </c>
-      <c r="T75" t="n">
-        <v>824627828.2</v>
-      </c>
-      <c r="U75" t="n">
-        <v>905873638</v>
-      </c>
-      <c r="V75" t="n">
-        <v>844221435.83</v>
-      </c>
-      <c r="W75" t="n">
-        <v>1022937269</v>
-      </c>
-      <c r="X75" t="n">
-        <v>1084029615</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>1191098183</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>1845137908.64</v>
-      </c>
-      <c r="AA75" t="n">
-        <v>1229743807</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>1804987860.82</v>
-      </c>
-      <c r="AC75" t="n">
-        <v>1329276535</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>1092808391.82</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>1551968629</v>
-      </c>
-      <c r="AF75" t="n">
-        <v>1693635287.04</v>
-      </c>
-      <c r="AG75" t="n">
-        <v>1481085981</v>
-      </c>
-      <c r="AH75" t="n">
-        <v>2539557566.72</v>
-      </c>
-      <c r="AI75" t="n">
-        <v>3355657685</v>
+        <v>3193876982</v>
       </c>
     </row>
   </sheetData>
@@ -21536,7 +19934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24029,10 +22427,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>-58</v>
+        <v>-29</v>
       </c>
       <c r="E64" t="n">
-        <v>-162951874</v>
+        <v>-81475937</v>
       </c>
       <c r="F64" t="n">
         <v>124</v>
@@ -24047,10 +22445,10 @@
         <v>9950909</v>
       </c>
       <c r="J64" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="K64" t="n">
-        <v>-85242406</v>
+        <v>-3766469</v>
       </c>
     </row>
     <row r="65">
@@ -24098,37 +22496,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IT-001</t>
+          <t>OTH-010</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Màn hình máy tính &amp; Tivi</t>
+          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>-490909</v>
+        <v>18182</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>6409091</v>
+        <v>18182</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>6900000</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>-981818</v>
+        <v>36364</v>
       </c>
     </row>
     <row r="67">
@@ -24137,12 +22535,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IT-003</t>
+          <t>OTH-073</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Máy quét văn bản (Scanner)</t>
+          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -24176,304 +22574,70 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VP-050</t>
+          <t>SRV-002</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nội thất &amp; Thiết bị văn phòng</t>
+          <t>Dịch vụ &amp; Thi công - 2025</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>-85242406</v>
+        <v>130000</v>
       </c>
       <c r="F68" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>87660377</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>9950909</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>174</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>-7532938</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>OTH-085</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Thiết bị liên lạc vô tuyến</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tổng cộng</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>207.89</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>21133196733</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>2119</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1852892781</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>562</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1195768183</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1764.89</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OTH-005</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Phí chuyển phát nhanh &amp; Giao nhận Logistics</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>OTH-010</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" t="n">
-        <v>18182</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>18182</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>2</v>
-      </c>
-      <c r="K71" t="n">
-        <v>36364</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>OTH-067</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Máy đếm tiền &amp; Thiết bị kiểm định tài chính</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OTH-073</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>SRV-002</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Dịch vụ &amp; Thi công - 2025</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10</v>
-      </c>
-      <c r="E74" t="n">
-        <v>130000</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>10</v>
-      </c>
-      <c r="K74" t="n">
-        <v>130000</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Tổng cộng</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="n">
-        <v>236.89</v>
-      </c>
-      <c r="E75" t="n">
-        <v>20965987481</v>
-      </c>
-      <c r="F75" t="n">
-        <v>2244</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1946962249</v>
-      </c>
-      <c r="H75" t="n">
-        <v>571</v>
-      </c>
-      <c r="I75" t="n">
-        <v>1212619092</v>
-      </c>
-      <c r="J75" t="n">
-        <v>1909.89</v>
-      </c>
-      <c r="K75" t="n">
-        <v>21700330638</v>
+        <v>21790321331</v>
       </c>
     </row>
   </sheetData>
@@ -24487,7 +22651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26905,7 +25069,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>-981818</v>
+        <v>-490909</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -26923,7 +25087,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>-981818</v>
+        <v>-490909</v>
       </c>
     </row>
     <row r="63">
@@ -26980,10 +25144,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="E64" t="n">
-        <v>-7532938</v>
+        <v>-3766469</v>
       </c>
       <c r="F64" t="n">
         <v>51</v>
@@ -26998,10 +25162,10 @@
         <v>50072728</v>
       </c>
       <c r="J64" t="n">
-        <v>156</v>
+        <v>69</v>
       </c>
       <c r="K64" t="n">
-        <v>-25473767</v>
+        <v>-21707298</v>
       </c>
     </row>
     <row r="65">
@@ -27049,25 +25213,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IT-001</t>
+          <t>OTH-010</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Màn hình máy tính &amp; Tivi</t>
+          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>-981818</v>
+        <v>36364</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>18182</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -27076,10 +25240,10 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K66" t="n">
-        <v>-981818</v>
+        <v>54546</v>
       </c>
     </row>
     <row r="67">
@@ -27088,12 +25252,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IT-003</t>
+          <t>OTH-073</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Máy quét văn bản (Scanner)</t>
+          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -27127,304 +25291,70 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VP-050</t>
+          <t>SRV-002</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nội thất &amp; Thiết bị văn phòng</t>
+          <t>Dịch vụ &amp; Thi công - 2025</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>-25473767</v>
+        <v>130000</v>
       </c>
       <c r="F68" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>32131899</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>50072728</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>-43414596</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>OTH-085</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Thiết bị liên lạc vô tuyến</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tổng cộng</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1764.89</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>21790321331</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1458.41</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1546332254.63</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1166</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1549732728</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>2057.3</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OTH-005</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Phí chuyển phát nhanh &amp; Giao nhận Logistics</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>OTH-010</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>2</v>
-      </c>
-      <c r="E71" t="n">
-        <v>36364</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>18182</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>3</v>
-      </c>
-      <c r="K71" t="n">
-        <v>54546</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>OTH-067</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Máy đếm tiền &amp; Thiết bị kiểm định tài chính</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OTH-073</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>SRV-002</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Dịch vụ &amp; Thi công - 2025</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10</v>
-      </c>
-      <c r="E74" t="n">
-        <v>130000</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>10</v>
-      </c>
-      <c r="K74" t="n">
-        <v>130000</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Tổng cộng</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="n">
-        <v>2007.89</v>
-      </c>
-      <c r="E75" t="n">
-        <v>21759608368</v>
-      </c>
-      <c r="F75" t="n">
-        <v>1509.41</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1578464153.63</v>
-      </c>
-      <c r="H75" t="n">
-        <v>1235</v>
-      </c>
-      <c r="I75" t="n">
-        <v>1599805456</v>
-      </c>
-      <c r="J75" t="n">
-        <v>2282.3</v>
-      </c>
-      <c r="K75" t="n">
-        <v>21738267065.63</v>
+        <v>21786920857.63</v>
       </c>
     </row>
   </sheetData>
@@ -27438,7 +25368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29856,7 +27786,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>-981818</v>
+        <v>-490909</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -29874,7 +27804,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>-981818</v>
+        <v>-490909</v>
       </c>
     </row>
     <row r="63">
@@ -29931,10 +27861,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="E64" t="n">
-        <v>-43414596</v>
+        <v>-21707298</v>
       </c>
       <c r="F64" t="n">
         <v>102</v>
@@ -29949,10 +27879,10 @@
         <v>43150003</v>
       </c>
       <c r="J64" t="n">
-        <v>194</v>
+        <v>125</v>
       </c>
       <c r="K64" t="n">
-        <v>18467703</v>
+        <v>40175001</v>
       </c>
     </row>
     <row r="65">
@@ -30000,25 +27930,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IT-001</t>
+          <t>OTH-010</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Màn hình máy tính &amp; Tivi</t>
+          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>-981818</v>
+        <v>54546</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>54545</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -30027,10 +27957,10 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K66" t="n">
-        <v>-981818</v>
+        <v>109091</v>
       </c>
     </row>
     <row r="67">
@@ -30039,12 +27969,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IT-003</t>
+          <t>OTH-073</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Máy quét văn bản (Scanner)</t>
+          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -30078,304 +28008,70 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VP-050</t>
+          <t>SRV-002</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nội thất &amp; Thiết bị văn phòng</t>
+          <t>Dịch vụ &amp; Thi công - 2025</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>194</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>18467703</v>
+        <v>130000</v>
       </c>
       <c r="F68" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>105032302</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>43150003</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>80350002</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>OTH-085</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Thiết bị liên lạc vô tuyến</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tổng cộng</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>2057.3</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>21786920857.63</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>927.73</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>816733309.09</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>638</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>978168179</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>2347.03</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OTH-005</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Phí chuyển phát nhanh &amp; Giao nhận Logistics</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>OTH-010</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>3</v>
-      </c>
-      <c r="E71" t="n">
-        <v>54546</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>54545</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>4</v>
-      </c>
-      <c r="K71" t="n">
-        <v>109091</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>OTH-067</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Máy đếm tiền &amp; Thiết bị kiểm định tài chính</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OTH-073</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>SRV-002</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Dịch vụ &amp; Thi công - 2025</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10</v>
-      </c>
-      <c r="E74" t="n">
-        <v>130000</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>10</v>
-      </c>
-      <c r="K74" t="n">
-        <v>130000</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Tổng cộng</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="n">
-        <v>2320.3</v>
-      </c>
-      <c r="E75" t="n">
-        <v>21782208535.63</v>
-      </c>
-      <c r="F75" t="n">
-        <v>1029.73</v>
-      </c>
-      <c r="G75" t="n">
-        <v>921765611.09</v>
-      </c>
-      <c r="H75" t="n">
-        <v>684</v>
-      </c>
-      <c r="I75" t="n">
-        <v>1021318182</v>
-      </c>
-      <c r="J75" t="n">
-        <v>2666.03</v>
-      </c>
-      <c r="K75" t="n">
-        <v>21682655964.72</v>
+        <v>21625485987.72</v>
       </c>
     </row>
   </sheetData>
@@ -30389,7 +28085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32807,7 +30503,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>-981818</v>
+        <v>-490909</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
@@ -32825,7 +30521,7 @@
         <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>5427273</v>
+        <v>5918182</v>
       </c>
     </row>
     <row r="63">
@@ -32882,10 +30578,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="E64" t="n">
-        <v>80350002</v>
+        <v>40175001</v>
       </c>
       <c r="F64" t="n">
         <v>74</v>
@@ -32900,10 +30596,10 @@
         <v>32409091</v>
       </c>
       <c r="J64" t="n">
-        <v>264</v>
+        <v>139</v>
       </c>
       <c r="K64" t="n">
-        <v>115539696.94</v>
+        <v>75364695.94</v>
       </c>
     </row>
     <row r="65">
@@ -32951,25 +30647,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IT-001</t>
+          <t>OTH-010</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Màn hình máy tính &amp; Tivi</t>
+          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>5427273</v>
+        <v>109091</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>6409091</v>
+        <v>54545</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -32978,10 +30674,10 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K66" t="n">
-        <v>11836364</v>
+        <v>163636</v>
       </c>
     </row>
     <row r="67">
@@ -32990,37 +30686,37 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IT-003</t>
+          <t>OTH-073</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Máy quét văn bản (Scanner)</t>
+          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
         </is>
       </c>
       <c r="D67" t="n">
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>-818181.6399999997</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>6363636.36</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>7181818</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>-1636363.279999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -33029,304 +30725,70 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VP-050</t>
+          <t>SRV-002</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nội thất &amp; Thiết bị văn phòng</t>
+          <t>Dịch vụ &amp; Thi công - 2025</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>264</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>115539696.94</v>
+        <v>130000</v>
       </c>
       <c r="F68" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>67598785.94</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>32409091</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>278</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>150729391.88</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>OTH-085</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Thiết bị liên lạc vô tuyến</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tổng cộng</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>9</v>
+        <v>2347.03</v>
       </c>
       <c r="E69" t="n">
-        <v>2515500</v>
+        <v>21625485987.72</v>
       </c>
       <c r="F69" t="n">
-        <v>9</v>
+        <v>950</v>
       </c>
       <c r="G69" t="n">
-        <v>2515500</v>
+        <v>741740814.9</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>729</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>866282729</v>
       </c>
       <c r="J69" t="n">
-        <v>18</v>
+        <v>2568.03</v>
       </c>
       <c r="K69" t="n">
-        <v>5031000</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OTH-005</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Phí chuyển phát nhanh &amp; Giao nhận Logistics</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>OTH-010</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>4</v>
-      </c>
-      <c r="E71" t="n">
-        <v>109091</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>54545</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>5</v>
-      </c>
-      <c r="K71" t="n">
-        <v>163636</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>OTH-067</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Máy đếm tiền &amp; Thiết bị kiểm định tài chính</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OTH-073</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>SRV-002</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Dịch vụ &amp; Thi công - 2025</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10</v>
-      </c>
-      <c r="E74" t="n">
-        <v>130000</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>10</v>
-      </c>
-      <c r="K74" t="n">
-        <v>130000</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Tổng cộng</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="n">
-        <v>2746.03</v>
-      </c>
-      <c r="E75" t="n">
-        <v>21787834368.02</v>
-      </c>
-      <c r="F75" t="n">
-        <v>1035</v>
-      </c>
-      <c r="G75" t="n">
-        <v>824627828.2</v>
-      </c>
-      <c r="H75" t="n">
-        <v>790</v>
-      </c>
-      <c r="I75" t="n">
-        <v>905873638</v>
-      </c>
-      <c r="J75" t="n">
-        <v>2991.03</v>
-      </c>
-      <c r="K75" t="n">
-        <v>21706588558.22001</v>
+        <v>21500944073.62</v>
       </c>
     </row>
   </sheetData>
@@ -33340,7 +30802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35755,10 +33217,10 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>11836364</v>
+        <v>5918182</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -35773,10 +33235,10 @@
         <v>6900000</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>4936364</v>
+        <v>-981818</v>
       </c>
     </row>
     <row r="63">
@@ -35797,7 +33259,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>-1636363.279999999</v>
+        <v>-818181.6399999997</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -35815,7 +33277,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>-1636363.279999999</v>
+        <v>-818181.6399999997</v>
       </c>
     </row>
     <row r="64">
@@ -35833,10 +33295,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>278</v>
+        <v>139</v>
       </c>
       <c r="E64" t="n">
-        <v>150729391.88</v>
+        <v>75364695.94</v>
       </c>
       <c r="F64" t="n">
         <v>80</v>
@@ -35851,10 +33313,10 @@
         <v>21985455</v>
       </c>
       <c r="J64" t="n">
-        <v>325</v>
+        <v>186</v>
       </c>
       <c r="K64" t="n">
-        <v>183966077.88</v>
+        <v>108601381.94</v>
       </c>
     </row>
     <row r="65">
@@ -35872,10 +33334,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E65" t="n">
-        <v>5031000</v>
+        <v>2515500</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -35890,10 +33352,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K65" t="n">
-        <v>5031000</v>
+        <v>2515500</v>
       </c>
     </row>
     <row r="66">
@@ -35902,37 +33364,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IT-001</t>
+          <t>OTH-010</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Màn hình máy tính &amp; Tivi</t>
+          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
         </is>
       </c>
       <c r="D66" t="n">
+        <v>5</v>
+      </c>
+      <c r="E66" t="n">
+        <v>163636</v>
+      </c>
+      <c r="F66" t="n">
         <v>1</v>
       </c>
-      <c r="E66" t="n">
-        <v>4936364</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>54545</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>6900000</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K66" t="n">
-        <v>-1963636</v>
+        <v>218181</v>
       </c>
     </row>
     <row r="67">
@@ -35941,37 +33403,37 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IT-003</t>
+          <t>OTH-073</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Máy quét văn bản (Scanner)</t>
+          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
         </is>
       </c>
       <c r="D67" t="n">
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>-1636363.279999999</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>3226364</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1863636</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>-1636363.279999999</v>
+        <v>1362728</v>
       </c>
     </row>
     <row r="68">
@@ -35980,304 +33442,70 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VP-050</t>
+          <t>SRV-002</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nội thất &amp; Thiết bị văn phòng</t>
+          <t>Dịch vụ &amp; Thi công - 2025</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>325</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>183966077.88</v>
+        <v>130000</v>
       </c>
       <c r="F68" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>55222141</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>21985455</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>372</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>217202763.88</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>OTH-085</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Thiết bị liên lạc vô tuyến</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tổng cộng</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>18</v>
+        <v>2568.03</v>
       </c>
       <c r="E69" t="n">
-        <v>5031000</v>
+        <v>21500944073.62</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>2181.22</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>788999294.83</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>615</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>994051814</v>
       </c>
       <c r="J69" t="n">
-        <v>18</v>
+        <v>4134.25</v>
       </c>
       <c r="K69" t="n">
-        <v>5031000</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OTH-005</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Phí chuyển phát nhanh &amp; Giao nhận Logistics</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>OTH-010</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>5</v>
-      </c>
-      <c r="E71" t="n">
-        <v>163636</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>54545</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>6</v>
-      </c>
-      <c r="K71" t="n">
-        <v>218181</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>OTH-067</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Máy đếm tiền &amp; Thiết bị kiểm định tài chính</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OTH-073</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="n">
-        <v>2</v>
-      </c>
-      <c r="G73" t="n">
-        <v>3226364</v>
-      </c>
-      <c r="H73" t="n">
-        <v>1</v>
-      </c>
-      <c r="I73" t="n">
-        <v>1863636</v>
-      </c>
-      <c r="J73" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" t="n">
-        <v>1362728</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>SRV-002</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Dịch vụ &amp; Thi công - 2025</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10</v>
-      </c>
-      <c r="E74" t="n">
-        <v>130000</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>10</v>
-      </c>
-      <c r="K74" t="n">
-        <v>130000</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Tổng cộng</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="n">
-        <v>3061.03</v>
-      </c>
-      <c r="E75" t="n">
-        <v>21776221348.52</v>
-      </c>
-      <c r="F75" t="n">
-        <v>2261.22</v>
-      </c>
-      <c r="G75" t="n">
-        <v>844221435.83</v>
-      </c>
-      <c r="H75" t="n">
-        <v>649</v>
-      </c>
-      <c r="I75" t="n">
-        <v>1022937269</v>
-      </c>
-      <c r="J75" t="n">
-        <v>4673.25</v>
-      </c>
-      <c r="K75" t="n">
-        <v>21597505515.35</v>
+        <v>21295891554.45</v>
       </c>
     </row>
   </sheetData>
@@ -36291,7 +33519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38709,7 +35937,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>-1963636</v>
+        <v>-981818</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -38727,7 +35955,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>-1963636</v>
+        <v>-981818</v>
       </c>
     </row>
     <row r="63">
@@ -38748,7 +35976,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>-1636363.279999999</v>
+        <v>-818181.6399999997</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -38766,7 +35994,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>-1636363.279999999</v>
+        <v>-818181.6399999997</v>
       </c>
     </row>
     <row r="64">
@@ -38784,10 +36012,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>372</v>
+        <v>186</v>
       </c>
       <c r="E64" t="n">
-        <v>217202763.88</v>
+        <v>108601381.94</v>
       </c>
       <c r="F64" t="n">
         <v>29</v>
@@ -38802,10 +36030,10 @@
         <v>27286363</v>
       </c>
       <c r="J64" t="n">
-        <v>340</v>
+        <v>154</v>
       </c>
       <c r="K64" t="n">
-        <v>219964214.88</v>
+        <v>111362832.94</v>
       </c>
     </row>
     <row r="65">
@@ -38823,10 +36051,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E65" t="n">
-        <v>5031000</v>
+        <v>2515500</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -38841,10 +36069,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K65" t="n">
-        <v>5031000</v>
+        <v>2515500</v>
       </c>
     </row>
     <row r="66">
@@ -38853,25 +36081,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IT-001</t>
+          <t>OTH-010</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Màn hình máy tính &amp; Tivi</t>
+          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E66" t="n">
-        <v>-1963636</v>
+        <v>218181</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>54545</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -38880,10 +36108,10 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K66" t="n">
-        <v>-1963636</v>
+        <v>272726</v>
       </c>
     </row>
     <row r="67">
@@ -38892,19 +36120,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IT-003</t>
+          <t>OTH-073</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Máy quét văn bản (Scanner)</t>
+          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>-1636363.279999999</v>
+        <v>1362728</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -38919,10 +36147,10 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>-1636363.279999999</v>
+        <v>1362728</v>
       </c>
     </row>
     <row r="68">
@@ -38931,304 +36159,70 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VP-050</t>
+          <t>SRV-002</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nội thất &amp; Thiết bị văn phòng</t>
+          <t>Dịch vụ &amp; Thi công - 2025</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>340</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>219964214.88</v>
+        <v>130000</v>
       </c>
       <c r="F68" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>30047814</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>27286363</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>308</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>222725665.88</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>OTH-085</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Thiết bị liên lạc vô tuyến</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tổng cộng</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>18</v>
+        <v>4134.25</v>
       </c>
       <c r="E69" t="n">
-        <v>5031000</v>
+        <v>21295891554.45</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1053981801</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>887</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1163811820</v>
       </c>
       <c r="J69" t="n">
-        <v>18</v>
+        <v>3767.25</v>
       </c>
       <c r="K69" t="n">
-        <v>5031000</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OTH-005</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Phí chuyển phát nhanh &amp; Giao nhận Logistics</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>OTH-010</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>6</v>
-      </c>
-      <c r="E71" t="n">
-        <v>218181</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>54545</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>7</v>
-      </c>
-      <c r="K71" t="n">
-        <v>272726</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>OTH-067</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Máy đếm tiền &amp; Thiết bị kiểm định tài chính</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OTH-073</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1362728</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" t="n">
-        <v>1362728</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>SRV-002</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Dịch vụ &amp; Thi công - 2025</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10</v>
-      </c>
-      <c r="E74" t="n">
-        <v>130000</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>10</v>
-      </c>
-      <c r="K74" t="n">
-        <v>130000</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Tổng cộng</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="n">
-        <v>4687.25</v>
-      </c>
-      <c r="E75" t="n">
-        <v>21626603652.35</v>
-      </c>
-      <c r="F75" t="n">
-        <v>549</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1084029615</v>
-      </c>
-      <c r="H75" t="n">
-        <v>948</v>
-      </c>
-      <c r="I75" t="n">
-        <v>1191098183</v>
-      </c>
-      <c r="J75" t="n">
-        <v>4288.25</v>
-      </c>
-      <c r="K75" t="n">
-        <v>21519535084.35</v>
+        <v>21186061535.45</v>
       </c>
     </row>
   </sheetData>
@@ -39242,7 +36236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41660,7 +38654,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>-1963636</v>
+        <v>-981818</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -41678,7 +38672,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>-1963636</v>
+        <v>-981818</v>
       </c>
     </row>
     <row r="63">
@@ -41699,7 +38693,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>-1636363.279999999</v>
+        <v>-818181.6399999997</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -41717,7 +38711,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>-1636363.279999999</v>
+        <v>-818181.6399999997</v>
       </c>
     </row>
     <row r="64">
@@ -41735,10 +38729,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>308</v>
+        <v>154</v>
       </c>
       <c r="E64" t="n">
-        <v>222725665.88</v>
+        <v>111362832.94</v>
       </c>
       <c r="F64" t="n">
         <v>89</v>
@@ -41753,10 +38747,10 @@
         <v>58330034</v>
       </c>
       <c r="J64" t="n">
-        <v>322</v>
+        <v>168</v>
       </c>
       <c r="K64" t="n">
-        <v>206590915.7</v>
+        <v>95228082.75999999</v>
       </c>
     </row>
     <row r="65">
@@ -41774,10 +38768,10 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E65" t="n">
-        <v>5031000</v>
+        <v>2515500</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -41792,10 +38786,10 @@
         <v>4418182</v>
       </c>
       <c r="J65" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>612818</v>
+        <v>-1902682</v>
       </c>
     </row>
     <row r="66">
@@ -41804,25 +38798,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IT-001</t>
+          <t>OTH-010</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Màn hình máy tính &amp; Tivi</t>
+          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E66" t="n">
-        <v>-1963636</v>
+        <v>272726</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>54545</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -41831,10 +38825,10 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K66" t="n">
-        <v>-1963636</v>
+        <v>327271</v>
       </c>
     </row>
     <row r="67">
@@ -41843,19 +38837,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IT-003</t>
+          <t>OTH-073</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Máy quét văn bản (Scanner)</t>
+          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>-1636363.279999999</v>
+        <v>1362728</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -41870,10 +38864,10 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>-1636363.279999999</v>
+        <v>1362728</v>
       </c>
     </row>
     <row r="68">
@@ -41882,304 +38876,70 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VP-050</t>
+          <t>SRV-002</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nội thất &amp; Thiết bị văn phòng</t>
+          <t>Dịch vụ &amp; Thi công - 2025</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>322</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>206590915.7</v>
+        <v>130000</v>
       </c>
       <c r="F68" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>42195283.82</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>58330034</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>336</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>190456165.52</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>OTH-085</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Thiết bị liên lạc vô tuyến</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tổng cộng</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>9</v>
+        <v>3767.25</v>
       </c>
       <c r="E69" t="n">
-        <v>612818</v>
+        <v>21186061535.45</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>2836.49</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1802942624.82</v>
       </c>
       <c r="H69" t="n">
-        <v>9</v>
+        <v>975</v>
       </c>
       <c r="I69" t="n">
-        <v>4418182</v>
+        <v>1166995591</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>5628.74</v>
       </c>
       <c r="K69" t="n">
-        <v>-3805364</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OTH-005</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Phí chuyển phát nhanh &amp; Giao nhận Logistics</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>OTH-010</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>7</v>
-      </c>
-      <c r="E71" t="n">
-        <v>272726</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>54545</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>8</v>
-      </c>
-      <c r="K71" t="n">
-        <v>327271</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>OTH-067</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Máy đếm tiền &amp; Thiết bị kiểm định tài chính</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OTH-073</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1362728</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" t="n">
-        <v>1362728</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>SRV-002</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Dịch vụ &amp; Thi công - 2025</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10</v>
-      </c>
-      <c r="E74" t="n">
-        <v>130000</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>10</v>
-      </c>
-      <c r="K74" t="n">
-        <v>130000</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Tổng cộng</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="n">
-        <v>4261.25</v>
-      </c>
-      <c r="E75" t="n">
-        <v>21501743603.17</v>
-      </c>
-      <c r="F75" t="n">
-        <v>2925.49</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1845137908.64</v>
-      </c>
-      <c r="H75" t="n">
-        <v>1059</v>
-      </c>
-      <c r="I75" t="n">
-        <v>1229743807</v>
-      </c>
-      <c r="J75" t="n">
-        <v>6127.74</v>
-      </c>
-      <c r="K75" t="n">
-        <v>22117137704.81</v>
+        <v>21822008569.27</v>
       </c>
     </row>
   </sheetData>
@@ -42193,7 +38953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44611,7 +41371,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>-1963636</v>
+        <v>-981818</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
@@ -44629,7 +41389,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>-11009091</v>
+        <v>-10027273</v>
       </c>
     </row>
     <row r="63">
@@ -44650,7 +41410,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>-1636363.279999999</v>
+        <v>-818181.6399999997</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -44668,7 +41428,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>-1636363.279999999</v>
+        <v>-818181.6399999997</v>
       </c>
     </row>
     <row r="64">
@@ -44686,10 +41446,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>336</v>
+        <v>168</v>
       </c>
       <c r="E64" t="n">
-        <v>190456165.52</v>
+        <v>95228082.75999999</v>
       </c>
       <c r="F64" t="n">
         <v>42</v>
@@ -44704,10 +41464,10 @@
         <v>15347274</v>
       </c>
       <c r="J64" t="n">
-        <v>359</v>
+        <v>191</v>
       </c>
       <c r="K64" t="n">
-        <v>201677234.52</v>
+        <v>106449151.76</v>
       </c>
     </row>
     <row r="65">
@@ -44728,7 +41488,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>-3805364</v>
+        <v>-1902682</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -44746,7 +41506,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>-3805364</v>
+        <v>-1902682</v>
       </c>
     </row>
     <row r="66">
@@ -44755,37 +41515,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IT-001</t>
+          <t>OTH-010</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Màn hình máy tính &amp; Tivi</t>
+          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E66" t="n">
-        <v>-11009091</v>
+        <v>327271</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>18090909</v>
+        <v>54545</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>27136364</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K66" t="n">
-        <v>-20054546</v>
+        <v>381816</v>
       </c>
     </row>
     <row r="67">
@@ -44794,25 +41554,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IT-003</t>
+          <t>OTH-073</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Máy quét văn bản (Scanner)</t>
+          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>-1636363.279999999</v>
+        <v>1362728</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>668182</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -44821,10 +41581,10 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>-1636363.279999999</v>
+        <v>2030910</v>
       </c>
     </row>
     <row r="68">
@@ -44833,304 +41593,70 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VP-050</t>
+          <t>SRV-002</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nội thất &amp; Thiết bị văn phòng</t>
+          <t>Dịch vụ &amp; Thi công - 2025</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>359</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>201677234.52</v>
+        <v>130000</v>
       </c>
       <c r="F68" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>26568343</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>15347274</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>382</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>212898303.52</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>OTH-085</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Thiết bị liên lạc vô tuyến</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tổng cộng</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>5628.74</v>
       </c>
       <c r="E69" t="n">
-        <v>-3805364</v>
+        <v>21822008569.27</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>2185.51</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1760328608.82</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>858</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1286792897</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>6956.25</v>
       </c>
       <c r="K69" t="n">
-        <v>-3805364</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>OTH-005</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Phí chuyển phát nhanh &amp; Giao nhận Logistics</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>OTH-010</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Dịch vụ tin nhắn thông báo (SMS Brandname)</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>8</v>
-      </c>
-      <c r="E71" t="n">
-        <v>327271</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>54545</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>9</v>
-      </c>
-      <c r="K71" t="n">
-        <v>381816</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>OTH-067</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Máy đếm tiền &amp; Thiết bị kiểm định tài chính</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>OTH-073</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Hạt mạng &amp; Đầu nối viễn thông chuẩn RJ45</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1362728</v>
-      </c>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" t="n">
-        <v>668182</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>2</v>
-      </c>
-      <c r="K73" t="n">
-        <v>2030910</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>SRV-002</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Dịch vụ &amp; Thi công - 2025</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10</v>
-      </c>
-      <c r="E74" t="n">
-        <v>130000</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>10</v>
-      </c>
-      <c r="K74" t="n">
-        <v>130000</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Tổng cộng</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="n">
-        <v>6155.74</v>
-      </c>
-      <c r="E75" t="n">
-        <v>22098760386.63</v>
-      </c>
-      <c r="F75" t="n">
-        <v>2228.51</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1804987860.82</v>
-      </c>
-      <c r="H75" t="n">
-        <v>878</v>
-      </c>
-      <c r="I75" t="n">
-        <v>1329276535</v>
-      </c>
-      <c r="J75" t="n">
-        <v>7506.25</v>
-      </c>
-      <c r="K75" t="n">
-        <v>22574471712.45</v>
+        <v>22295544281.09</v>
       </c>
     </row>
   </sheetData>

--- a/docs/huyvu/XNT_HuyVu_2023.xlsx
+++ b/docs/huyvu/XNT_HuyVu_2023.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tháng 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tháng 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Tháng 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Tháng 4" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tháng 5" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Tháng 6" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Tháng 7" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Tháng 8" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Tháng 9" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Tháng 10" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Tháng 11" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Tháng 12" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Hoadon" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="xnt12thang" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 6" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 7" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 8" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 9" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 10" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 11" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 12" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoadon" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="xnt12thang" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2454,7 +2454,7 @@
         <v>38</v>
       </c>
       <c r="E52" t="n">
-        <v>63910517.26693878</v>
+        <v>63910517.26693877</v>
       </c>
       <c r="F52" t="n">
         <v>11</v>
@@ -29068,7 +29068,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>63910517.26693878</v>
+        <v>63910517.26693877</v>
       </c>
       <c r="D52" t="n">
         <v>67317022</v>

--- a/docs/huyvu/XNT_HuyVu_2023.xlsx
+++ b/docs/huyvu/XNT_HuyVu_2023.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="xnt12thang" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tháng 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Tháng 2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Tháng 3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tháng 4" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Tháng 5" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Tháng 6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Tháng 7" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Tháng 8" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Tháng 9" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Tháng 10" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Tháng 11" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Tháng 12" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Hoadon" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="xnt12thang" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 8" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 9" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 10" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 11" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tháng 12" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoadon" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
